--- a/Stocks/META.xlsx
+++ b/Stocks/META.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://academiafaedupt-my.sharepoint.com/personal/sbclemente_academiafa_edu_pt/Documents/Gigs/WorkingFolder/Finance/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://academiafaedupt-my.sharepoint.com/personal/sbclemente_academiafa_edu_pt/Documents/Gigs/WorkingFolder/Finance_Shared/Stocks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{91A85DBD-37F5-495F-9D0D-AFC39F49FA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66850A6C-FB13-42C1-8567-B03F7E006BE8}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="8_{91A85DBD-37F5-495F-9D0D-AFC39F49FA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4145732-E596-4F2E-ABBA-C8873E9A6337}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{A4478C07-9115-4914-9DE9-A3B7CC45EB27}"/>
+    <workbookView xWindow="6390" yWindow="6000" windowWidth="18225" windowHeight="9480" activeTab="1" xr2:uid="{A4478C07-9115-4914-9DE9-A3B7CC45EB27}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
   <si>
     <t>META</t>
   </si>
@@ -349,6 +349,12 @@
   </si>
   <si>
     <t>CapeX</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -544,10 +550,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1050,6 +1052,12 @@
       <c r="Q2" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="R2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="Y2" s="2">
         <v>2022</v>
       </c>
@@ -1135,8 +1143,11 @@
       <c r="P3" s="3">
         <v>51242</v>
       </c>
-      <c r="Q3" s="3" t="s">
-        <v>9</v>
+      <c r="Q3" s="3">
+        <v>59893</v>
+      </c>
+      <c r="R3" s="3">
+        <v>56311</v>
       </c>
       <c r="Y3" s="3">
         <f>SUM(B3:E3)</f>
@@ -1151,28 +1162,28 @@
         <v>164500</v>
       </c>
       <c r="AB3" s="3">
-        <f>+AA1*1.2</f>
-        <v>194257.43999999997</v>
+        <f>+SUM(N3:Q3)</f>
+        <v>200965</v>
       </c>
       <c r="AC3" s="3">
         <f>+AB3*1.2</f>
-        <v>233108.92799999996</v>
+        <v>241158</v>
       </c>
       <c r="AD3" s="3">
         <f>+AC3*1.2</f>
-        <v>279730.71359999996</v>
+        <v>289389.59999999998</v>
       </c>
       <c r="AE3" s="3">
         <f>+AD3*1.2</f>
-        <v>335676.85631999996</v>
+        <v>347267.51999999996</v>
       </c>
       <c r="AF3" s="3">
         <f t="shared" ref="AF3:AG3" si="1">+AE3*1.15</f>
-        <v>386028.38476799993</v>
+        <v>399357.64799999993</v>
       </c>
       <c r="AG3" s="3">
         <f t="shared" si="1"/>
-        <v>443932.64248319989</v>
+        <v>459261.29519999988</v>
       </c>
     </row>
     <row r="4" spans="1:65" ht="15" x14ac:dyDescent="0.25">
@@ -1224,6 +1235,12 @@
       <c r="P4" s="2">
         <v>9206</v>
       </c>
+      <c r="Q4" s="2">
+        <v>35148</v>
+      </c>
+      <c r="R4" s="2">
+        <v>33439</v>
+      </c>
       <c r="V4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1317,7 +1334,7 @@
         <v>39546</v>
       </c>
       <c r="N5" s="3">
-        <f t="shared" ref="N5:P5" si="5">+N3-N4</f>
+        <f t="shared" ref="N5:R5" si="5">+N3-N4</f>
         <v>34742</v>
       </c>
       <c r="O5" s="3">
@@ -1328,6 +1345,14 @@
         <f t="shared" si="5"/>
         <v>42036</v>
       </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="5"/>
+        <v>24745</v>
+      </c>
+      <c r="R5" s="3">
+        <f t="shared" si="5"/>
+        <v>22872</v>
+      </c>
       <c r="W5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1345,27 +1370,27 @@
       </c>
       <c r="AB5" s="3">
         <f t="shared" ref="AB5:AG5" si="6">+AB3-AB4</f>
-        <v>161079.23999999996</v>
+        <v>167786.8</v>
       </c>
       <c r="AC5" s="3">
         <f t="shared" si="6"/>
-        <v>196612.90799999994</v>
+        <v>204661.97999999998</v>
       </c>
       <c r="AD5" s="3">
         <f t="shared" si="6"/>
-        <v>239585.09159999993</v>
+        <v>249243.97799999994</v>
       </c>
       <c r="AE5" s="3">
         <f t="shared" si="6"/>
-        <v>291516.67211999994</v>
+        <v>303107.33579999994</v>
       </c>
       <c r="AF5" s="3">
         <f t="shared" si="6"/>
-        <v>337452.18214799988</v>
+        <v>350781.44537999987</v>
       </c>
       <c r="AG5" s="3">
         <f t="shared" si="6"/>
-        <v>390498.81960119982</v>
+        <v>405827.47231799981</v>
       </c>
     </row>
     <row r="6" spans="1:65" x14ac:dyDescent="0.2">
@@ -1433,28 +1458,28 @@
         <v>43872</v>
       </c>
       <c r="AB6" s="2">
-        <f t="shared" ref="AB6:AG6" si="8">+AA6*1.05</f>
-        <v>46065.599999999999</v>
+        <f>+AA6*1.08</f>
+        <v>47381.760000000002</v>
       </c>
       <c r="AC6" s="2">
-        <f t="shared" si="8"/>
-        <v>48368.88</v>
+        <f t="shared" ref="AC6:AG6" si="8">+AB6*1.08</f>
+        <v>51172.300800000005</v>
       </c>
       <c r="AD6" s="2">
         <f t="shared" si="8"/>
-        <v>50787.324000000001</v>
+        <v>55266.084864000011</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="8"/>
-        <v>53326.690200000005</v>
+        <v>59687.371653120019</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="8"/>
-        <v>55993.024710000005</v>
+        <v>64462.361385369622</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="8"/>
-        <v>58792.675945500006</v>
+        <v>69619.350296199191</v>
       </c>
     </row>
     <row r="7" spans="1:65" x14ac:dyDescent="0.2">
@@ -1519,11 +1544,11 @@
         <v>11347</v>
       </c>
       <c r="AB7" s="2">
-        <f t="shared" ref="AB7:AG7" si="9">+AA7*1.03</f>
+        <f>+AA7*1.03</f>
         <v>11687.41</v>
       </c>
       <c r="AC7" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="AC7:AG7" si="9">+AB7*1.03</f>
         <v>12038.032300000001</v>
       </c>
       <c r="AD7" s="2">
@@ -1605,28 +1630,28 @@
         <v>9739</v>
       </c>
       <c r="AB8" s="2">
-        <f t="shared" ref="AB8:AG8" si="10">+AA8</f>
-        <v>9739</v>
+        <f>+AA8*1.03</f>
+        <v>10031.17</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" si="10"/>
-        <v>9739</v>
+        <f t="shared" ref="AC8:AG8" si="10">+AB8*1.03</f>
+        <v>10332.105100000001</v>
       </c>
       <c r="AD8" s="2">
         <f t="shared" si="10"/>
-        <v>9739</v>
+        <v>10642.068253000001</v>
       </c>
       <c r="AE8" s="2">
         <f t="shared" si="10"/>
-        <v>9739</v>
+        <v>10961.330300590002</v>
       </c>
       <c r="AF8" s="2">
         <f t="shared" si="10"/>
-        <v>9739</v>
+        <v>11290.170209607702</v>
       </c>
       <c r="AG8" s="2">
         <f t="shared" si="10"/>
-        <v>9739</v>
+        <v>11628.875315895933</v>
       </c>
     </row>
     <row r="9" spans="1:65" x14ac:dyDescent="0.2">
@@ -1702,32 +1727,32 @@
         <v>62192</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" ref="AA9" si="15">+AA6+AA7+AA8</f>
+        <f t="shared" ref="AA9:AG9" si="15">+AA6+AA7+AA8</f>
         <v>64958</v>
       </c>
       <c r="AB9" s="2">
-        <f t="shared" si="14"/>
-        <v>67492.009999999995</v>
+        <f t="shared" si="15"/>
+        <v>69100.34</v>
       </c>
       <c r="AC9" s="2">
-        <f t="shared" si="14"/>
-        <v>70145.912299999996</v>
+        <f t="shared" si="15"/>
+        <v>73542.438200000004</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" si="14"/>
-        <v>72925.497269</v>
+        <f t="shared" si="15"/>
+        <v>78307.326386000015</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="14"/>
-        <v>75836.838667069998</v>
+        <f t="shared" si="15"/>
+        <v>83419.850420780014</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="14"/>
-        <v>78886.307631082105</v>
+        <f t="shared" si="15"/>
+        <v>88906.814516059429</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" ref="AG9" si="16">+AG6+AG7+AG8</f>
-        <v>82080.587354214571</v>
+        <f t="shared" si="15"/>
+        <v>94797.137020809678</v>
       </c>
     </row>
     <row r="10" spans="1:65" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -1735,100 +1760,100 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <f t="shared" ref="B10:L10" si="17">+B5-B9</f>
+        <f t="shared" ref="B10:L10" si="16">+B5-B9</f>
         <v>8524</v>
       </c>
       <c r="C10" s="3">
+        <f t="shared" si="16"/>
+        <v>8358</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="16"/>
+        <v>5664</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="16"/>
+        <v>6399</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="16"/>
+        <v>7227</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="16"/>
+        <v>9392</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="16"/>
+        <v>13748</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="16"/>
+        <v>16384</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="16"/>
+        <v>13818</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="16"/>
+        <v>14847</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="16"/>
+        <v>17350</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" ref="M10:N10" si="17">+M5-M9</f>
+        <v>23365</v>
+      </c>
+      <c r="N10" s="3">
         <f t="shared" si="17"/>
-        <v>8358</v>
-      </c>
-      <c r="D10" s="3">
-        <f t="shared" si="17"/>
-        <v>5664</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="17"/>
-        <v>6399</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="17"/>
-        <v>7227</v>
-      </c>
-      <c r="G10" s="3">
-        <f t="shared" si="17"/>
-        <v>9392</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="17"/>
-        <v>13748</v>
-      </c>
-      <c r="I10" s="3">
-        <f t="shared" si="17"/>
-        <v>16384</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="17"/>
-        <v>13818</v>
-      </c>
-      <c r="K10" s="3">
-        <f t="shared" si="17"/>
-        <v>14847</v>
-      </c>
-      <c r="L10" s="3">
-        <f t="shared" si="17"/>
-        <v>17350</v>
-      </c>
-      <c r="M10" s="3">
-        <f t="shared" ref="M10:N10" si="18">+M5-M9</f>
-        <v>23365</v>
-      </c>
-      <c r="N10" s="3">
+        <v>17555</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" ref="O10:P10" si="18">+O5-O9</f>
+        <v>20441</v>
+      </c>
+      <c r="P10" s="3">
         <f t="shared" si="18"/>
-        <v>17555</v>
-      </c>
-      <c r="O10" s="3">
-        <f t="shared" ref="O10:P10" si="19">+O5-O9</f>
-        <v>20441</v>
-      </c>
-      <c r="P10" s="3">
+        <v>20535</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" ref="Y10:AF10" si="19">+Y5-Y9</f>
+        <v>28945</v>
+      </c>
+      <c r="Z10" s="3">
         <f t="shared" si="19"/>
-        <v>20535</v>
-      </c>
-      <c r="Y10" s="3">
-        <f t="shared" ref="Y10:AF10" si="20">+Y5-Y9</f>
-        <v>28945</v>
-      </c>
-      <c r="Z10" s="3">
-        <f t="shared" si="20"/>
         <v>46751</v>
       </c>
       <c r="AA10" s="3">
-        <f t="shared" ref="AA10" si="21">+AA5-AA9</f>
+        <f t="shared" ref="AA10:AG10" si="20">+AA5-AA9</f>
         <v>69380</v>
       </c>
       <c r="AB10" s="3">
         <f t="shared" si="20"/>
-        <v>93587.229999999967</v>
+        <v>98686.459999999992</v>
       </c>
       <c r="AC10" s="3">
         <f t="shared" si="20"/>
-        <v>126466.99569999994</v>
+        <v>131119.54179999998</v>
       </c>
       <c r="AD10" s="3">
         <f t="shared" si="20"/>
-        <v>166659.59433099994</v>
+        <v>170936.65161399991</v>
       </c>
       <c r="AE10" s="3">
         <f t="shared" si="20"/>
-        <v>215679.83345292995</v>
+        <v>219687.48537921993</v>
       </c>
       <c r="AF10" s="3">
         <f t="shared" si="20"/>
-        <v>258565.87451691777</v>
+        <v>261874.63086394046</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" ref="AG10" si="22">+AG5-AG9</f>
-        <v>308418.23224698525</v>
+        <f t="shared" si="20"/>
+        <v>311030.33529719012</v>
       </c>
     </row>
     <row r="11" spans="1:65" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1897,32 +1922,32 @@
         <v>931.40000000000009</v>
       </c>
       <c r="AA11" s="6">
-        <f t="shared" ref="AA11:AA13" si="23">SUM(J11:M11)</f>
+        <f t="shared" ref="AA11:AA13" si="21">SUM(J11:M11)</f>
         <v>1284</v>
       </c>
       <c r="AB11" s="6">
-        <f>+Z33*$V$15</f>
-        <v>931.40000000000009</v>
+        <f>+AA33*0.03</f>
+        <v>2429.64</v>
       </c>
       <c r="AC11" s="6">
-        <f t="shared" ref="AC11:AG11" si="24">+AA33*$V$15</f>
-        <v>4049.4</v>
+        <f t="shared" ref="AC11:AG11" si="22">+AB33*0.03</f>
+        <v>4856.4264000000003</v>
       </c>
       <c r="AD11" s="6">
-        <f t="shared" si="24"/>
-        <v>7830.145199999999</v>
+        <f t="shared" si="22"/>
+        <v>8119.8496367999996</v>
       </c>
       <c r="AE11" s="6">
-        <f t="shared" si="24"/>
-        <v>13050.801027999996</v>
+        <f t="shared" si="22"/>
+        <v>12417.205666819198</v>
       </c>
       <c r="AF11" s="6">
-        <f t="shared" si="24"/>
-        <v>20030.390609239996</v>
+        <f t="shared" si="22"/>
+        <v>17987.718251924136</v>
       </c>
       <c r="AG11" s="6">
-        <f t="shared" si="24"/>
-        <v>29179.615988477191</v>
+        <f t="shared" si="22"/>
+        <v>24704.414630704887</v>
       </c>
     </row>
     <row r="12" spans="1:65" x14ac:dyDescent="0.2">
@@ -1930,67 +1955,67 @@
         <v>26</v>
       </c>
       <c r="B12" s="2">
-        <f t="shared" ref="B12:L12" si="25">+B10+B11</f>
+        <f t="shared" ref="B12:L12" si="23">+B10+B11</f>
         <v>8908</v>
       </c>
       <c r="C12" s="2">
+        <f t="shared" si="23"/>
+        <v>8186</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="23"/>
+        <v>5576</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="23"/>
+        <v>6149</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="23"/>
+        <v>7307</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="23"/>
+        <v>9293</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="23"/>
+        <v>14020</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="23"/>
+        <v>16808</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="23"/>
+        <v>14183</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" si="23"/>
+        <v>15106</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="23"/>
+        <v>17822</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" ref="M12:N12" si="24">+M10+M11</f>
+        <v>23553</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="24"/>
+        <v>18382</v>
+      </c>
+      <c r="O12" s="2">
+        <f t="shared" ref="O12:P12" si="25">+O10+O11</f>
+        <v>20534</v>
+      </c>
+      <c r="P12" s="2">
         <f t="shared" si="25"/>
-        <v>8186</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="25"/>
-        <v>5576</v>
-      </c>
-      <c r="E12" s="2">
-        <f t="shared" si="25"/>
-        <v>6149</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="25"/>
-        <v>7307</v>
-      </c>
-      <c r="G12" s="2">
-        <f t="shared" si="25"/>
-        <v>9293</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" si="25"/>
-        <v>14020</v>
-      </c>
-      <c r="I12" s="2">
-        <f t="shared" si="25"/>
-        <v>16808</v>
-      </c>
-      <c r="J12" s="2">
-        <f t="shared" si="25"/>
-        <v>14183</v>
-      </c>
-      <c r="K12" s="2">
-        <f t="shared" si="25"/>
-        <v>15106</v>
-      </c>
-      <c r="L12" s="2">
-        <f t="shared" si="25"/>
-        <v>17822</v>
-      </c>
-      <c r="M12" s="2">
-        <f t="shared" ref="M12:N12" si="26">+M10+M11</f>
-        <v>23553</v>
-      </c>
-      <c r="N12" s="2">
-        <f t="shared" si="26"/>
-        <v>18382</v>
-      </c>
-      <c r="O12" s="2">
-        <f t="shared" ref="O12:P12" si="27">+O10+O11</f>
-        <v>20534</v>
-      </c>
-      <c r="P12" s="2">
-        <f t="shared" si="27"/>
         <v>21663</v>
       </c>
       <c r="Y12" s="2">
-        <f t="shared" ref="Y12:AF12" si="28">+Y10+Y11</f>
+        <f t="shared" ref="Y12:AF12" si="26">+Y10+Y11</f>
         <v>28819</v>
       </c>
       <c r="Z12" s="2">
@@ -2002,28 +2027,28 @@
         <v>70664</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" si="28"/>
-        <v>94518.629999999961</v>
+        <f t="shared" ref="AB12:AG12" si="27">+AB10+AB11</f>
+        <v>101116.09999999999</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="28"/>
-        <v>130516.39569999994</v>
+        <f t="shared" si="27"/>
+        <v>135975.96819999997</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" si="28"/>
-        <v>174489.73953099994</v>
+        <f t="shared" si="27"/>
+        <v>179056.50125079992</v>
       </c>
       <c r="AE12" s="2">
-        <f t="shared" si="28"/>
-        <v>228730.63448092993</v>
+        <f t="shared" si="27"/>
+        <v>232104.69104603914</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" si="28"/>
-        <v>278596.26512615778</v>
+        <f t="shared" si="27"/>
+        <v>279862.34911586461</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" ref="AG12" si="29">+AG10+AG11</f>
-        <v>337597.84823546244</v>
+        <f t="shared" si="27"/>
+        <v>335734.74992789503</v>
       </c>
     </row>
     <row r="13" spans="1:65" x14ac:dyDescent="0.2">
@@ -2084,32 +2109,32 @@
         <v>8331</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="21"/>
         <v>8304</v>
       </c>
       <c r="AB13" s="2">
-        <f t="shared" ref="AB13:AF13" si="30">+AB12*0.2</f>
-        <v>18903.725999999991</v>
+        <f>+AB12*0.2</f>
+        <v>20223.22</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="30"/>
-        <v>26103.279139999988</v>
+        <f t="shared" ref="AC13:AG13" si="28">+AC12*0.2</f>
+        <v>27195.193639999998</v>
       </c>
       <c r="AD13" s="2">
-        <f t="shared" si="30"/>
-        <v>34897.947906199988</v>
+        <f t="shared" si="28"/>
+        <v>35811.300250159984</v>
       </c>
       <c r="AE13" s="2">
-        <f t="shared" si="30"/>
-        <v>45746.12689618599</v>
+        <f t="shared" si="28"/>
+        <v>46420.93820920783</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" si="30"/>
-        <v>55719.253025231563</v>
+        <f t="shared" si="28"/>
+        <v>55972.469823172927</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" ref="AG13" si="31">+AG12*0.2</f>
-        <v>67519.569647092489</v>
+        <f t="shared" si="28"/>
+        <v>67146.949985579005</v>
       </c>
     </row>
     <row r="14" spans="1:65" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -2117,234 +2142,237 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <f t="shared" ref="B14:L14" si="32">+B12-B13</f>
+        <f t="shared" ref="B14:L14" si="29">+B12-B13</f>
         <v>7465</v>
       </c>
       <c r="C14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>6687</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>4395</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>4652</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>5709</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>7788</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>11583</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>14017</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>12369</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>13465</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="29"/>
         <v>15688</v>
       </c>
       <c r="M14" s="3">
-        <f t="shared" ref="M14:N14" si="33">+M12-M13</f>
+        <f t="shared" ref="M14:N14" si="30">+M12-M13</f>
         <v>20838</v>
       </c>
       <c r="N14" s="3">
-        <f t="shared" si="33"/>
+        <f t="shared" si="30"/>
         <v>16644</v>
       </c>
       <c r="O14" s="3">
-        <f t="shared" ref="O14:P14" si="34">+O12-O13</f>
+        <f t="shared" ref="O14:P14" si="31">+O12-O13</f>
         <v>18337</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>2709</v>
       </c>
       <c r="Q14" s="3">
-        <v>24000</v>
+        <v>22768</v>
+      </c>
+      <c r="R14" s="3">
+        <v>26773</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="Y14" s="3">
-        <f t="shared" ref="Y14:AF14" si="35">+Y12-Y13</f>
+        <f t="shared" ref="Y14:AF14" si="32">+Y12-Y13</f>
         <v>23199</v>
       </c>
       <c r="Z14" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>39351.4</v>
       </c>
       <c r="AA14" s="3">
-        <f t="shared" si="35"/>
+        <f t="shared" si="32"/>
         <v>62360</v>
       </c>
       <c r="AB14" s="3">
-        <f t="shared" si="35"/>
-        <v>75614.903999999966</v>
+        <f>+AB12-AB13</f>
+        <v>80892.87999999999</v>
       </c>
       <c r="AC14" s="3">
-        <f t="shared" si="35"/>
-        <v>104413.11655999995</v>
+        <f t="shared" ref="AC14:AG14" si="33">+AC12-AC13</f>
+        <v>108780.77455999998</v>
       </c>
       <c r="AD14" s="3">
-        <f t="shared" si="35"/>
-        <v>139591.79162479995</v>
+        <f t="shared" si="33"/>
+        <v>143245.20100063994</v>
       </c>
       <c r="AE14" s="3">
-        <f t="shared" si="35"/>
-        <v>182984.50758474396</v>
+        <f t="shared" si="33"/>
+        <v>185683.75283683132</v>
       </c>
       <c r="AF14" s="3">
-        <f t="shared" si="35"/>
-        <v>222877.01210092622</v>
+        <f t="shared" si="33"/>
+        <v>223889.87929269168</v>
       </c>
       <c r="AG14" s="3">
-        <f t="shared" ref="AG14" si="36">+AG12-AG13</f>
-        <v>270078.27858836995</v>
+        <f t="shared" si="33"/>
+        <v>268587.79994231602</v>
       </c>
       <c r="AH14" s="3">
         <f>+AG14*(1-$V$16)</f>
-        <v>267377.49580248626</v>
+        <v>265901.92194289283</v>
       </c>
       <c r="AI14" s="3">
-        <f t="shared" ref="AI14:BM14" si="37">+AH14*(1-$V$16)</f>
-        <v>264703.72084446141</v>
+        <f t="shared" ref="AI14:BM14" si="34">+AH14*(1-$V$16)</f>
+        <v>263242.90272346389</v>
       </c>
       <c r="AJ14" s="3">
-        <f t="shared" si="37"/>
-        <v>262056.68363601679</v>
+        <f t="shared" si="34"/>
+        <v>260610.47369622925</v>
       </c>
       <c r="AK14" s="3">
-        <f t="shared" si="37"/>
-        <v>259436.11679965662</v>
+        <f t="shared" si="34"/>
+        <v>258004.36895926695</v>
       </c>
       <c r="AL14" s="3">
-        <f t="shared" si="37"/>
-        <v>256841.75563166005</v>
+        <f t="shared" si="34"/>
+        <v>255424.32526967427</v>
       </c>
       <c r="AM14" s="3">
-        <f t="shared" si="37"/>
-        <v>254273.33807534346</v>
+        <f t="shared" si="34"/>
+        <v>252870.08201697754</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="37"/>
-        <v>251730.60469459003</v>
+        <f t="shared" si="34"/>
+        <v>250341.38119680775</v>
       </c>
       <c r="AO14" s="3">
-        <f t="shared" si="37"/>
-        <v>249213.29864764411</v>
+        <f t="shared" si="34"/>
+        <v>247837.96738483966</v>
       </c>
       <c r="AP14" s="3">
-        <f t="shared" si="37"/>
-        <v>246721.16566116767</v>
+        <f t="shared" si="34"/>
+        <v>245359.58771099127</v>
       </c>
       <c r="AQ14" s="3">
-        <f t="shared" si="37"/>
-        <v>244253.954004556</v>
+        <f t="shared" si="34"/>
+        <v>242905.99183388136</v>
       </c>
       <c r="AR14" s="3">
-        <f t="shared" si="37"/>
-        <v>241811.41446451042</v>
+        <f t="shared" si="34"/>
+        <v>240476.93191554255</v>
       </c>
       <c r="AS14" s="3">
-        <f t="shared" si="37"/>
-        <v>239393.30031986532</v>
+        <f t="shared" si="34"/>
+        <v>238072.16259638712</v>
       </c>
       <c r="AT14" s="3">
-        <f t="shared" si="37"/>
-        <v>236999.36731666667</v>
+        <f t="shared" si="34"/>
+        <v>235691.44097042325</v>
       </c>
       <c r="AU14" s="3">
-        <f t="shared" si="37"/>
-        <v>234629.3736435</v>
+        <f t="shared" si="34"/>
+        <v>233334.52656071901</v>
       </c>
       <c r="AV14" s="3">
-        <f t="shared" si="37"/>
-        <v>232283.079907065</v>
+        <f t="shared" si="34"/>
+        <v>231001.1812951118</v>
       </c>
       <c r="AW14" s="3">
-        <f t="shared" si="37"/>
-        <v>229960.24910799434</v>
+        <f t="shared" si="34"/>
+        <v>228691.16948216068</v>
       </c>
       <c r="AX14" s="3">
-        <f t="shared" si="37"/>
-        <v>227660.6466169144</v>
+        <f t="shared" si="34"/>
+        <v>226404.25778733907</v>
       </c>
       <c r="AY14" s="3">
-        <f t="shared" si="37"/>
-        <v>225384.04015074525</v>
+        <f t="shared" si="34"/>
+        <v>224140.21520946568</v>
       </c>
       <c r="AZ14" s="3">
-        <f t="shared" si="37"/>
-        <v>223130.1997492378</v>
+        <f t="shared" si="34"/>
+        <v>221898.81305737101</v>
       </c>
       <c r="BA14" s="3">
-        <f t="shared" si="37"/>
-        <v>220898.89775174542</v>
+        <f t="shared" si="34"/>
+        <v>219679.8249267973</v>
       </c>
       <c r="BB14" s="3">
-        <f t="shared" si="37"/>
-        <v>218689.90877422795</v>
+        <f t="shared" si="34"/>
+        <v>217483.02667752933</v>
       </c>
       <c r="BC14" s="3">
-        <f t="shared" si="37"/>
-        <v>216503.00968648566</v>
+        <f t="shared" si="34"/>
+        <v>215308.19641075403</v>
       </c>
       <c r="BD14" s="3">
-        <f t="shared" si="37"/>
-        <v>214337.97958962081</v>
+        <f t="shared" si="34"/>
+        <v>213155.11444664648</v>
       </c>
       <c r="BE14" s="3">
-        <f t="shared" si="37"/>
-        <v>212194.5997937246</v>
+        <f t="shared" si="34"/>
+        <v>211023.56330218</v>
       </c>
       <c r="BF14" s="3">
-        <f t="shared" si="37"/>
-        <v>210072.65379578734</v>
+        <f t="shared" si="34"/>
+        <v>208913.3276691582</v>
       </c>
       <c r="BG14" s="3">
-        <f t="shared" si="37"/>
-        <v>207971.92725782946</v>
+        <f t="shared" si="34"/>
+        <v>206824.19439246663</v>
       </c>
       <c r="BH14" s="3">
-        <f t="shared" si="37"/>
-        <v>205892.20798525115</v>
+        <f t="shared" si="34"/>
+        <v>204755.95244854197</v>
       </c>
       <c r="BI14" s="3">
-        <f t="shared" si="37"/>
-        <v>203833.28590539863</v>
+        <f t="shared" si="34"/>
+        <v>202708.39292405653</v>
       </c>
       <c r="BJ14" s="3">
-        <f t="shared" si="37"/>
-        <v>201794.95304634466</v>
+        <f t="shared" si="34"/>
+        <v>200681.30899481598</v>
       </c>
       <c r="BK14" s="3">
-        <f t="shared" si="37"/>
-        <v>199777.0035158812</v>
+        <f t="shared" si="34"/>
+        <v>198674.49590486783</v>
       </c>
       <c r="BL14" s="3">
-        <f t="shared" si="37"/>
-        <v>197779.23348072238</v>
+        <f t="shared" si="34"/>
+        <v>196687.75094581913</v>
       </c>
       <c r="BM14" s="3">
-        <f t="shared" si="37"/>
-        <v>195801.44114591516</v>
+        <f t="shared" si="34"/>
+        <v>194720.87343636094</v>
       </c>
     </row>
     <row r="15" spans="1:65" x14ac:dyDescent="0.2">
@@ -2352,59 +2380,59 @@
         <v>29</v>
       </c>
       <c r="B15" s="4">
-        <f t="shared" ref="B15:L15" si="38">+B14/B16</f>
+        <f t="shared" ref="B15:L15" si="35">+B14/B16</f>
         <v>2.7394495412844035</v>
       </c>
       <c r="C15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>2.4730029585798818</v>
       </c>
       <c r="D15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>1.638702460850112</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>1.7634571645185746</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>2.206803247004252</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>4.4965062111801242</v>
       </c>
       <c r="I15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>5.4625876851130162</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>4.8601178781925345</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>5.3137332280978686</v>
       </c>
       <c r="L15" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="35"/>
         <v>6.2032423882957692</v>
       </c>
       <c r="M15" s="4">
-        <f t="shared" ref="M15:N15" si="39">+M14/M16</f>
+        <f t="shared" ref="M15:N15" si="36">+M14/M16</f>
         <v>8.2396204033214708</v>
       </c>
       <c r="N15" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="36"/>
         <v>6.5864661654135341</v>
       </c>
       <c r="O15" s="4">
-        <f t="shared" ref="O15" si="40">+O14/O16</f>
+        <f t="shared" ref="O15" si="37">+O14/O16</f>
         <v>7.2823669579030978</v>
       </c>
       <c r="P15" s="2">
@@ -2418,40 +2446,16 @@
         <v>0.05</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" ref="Y15:AF15" si="41">+Y14/Y16</f>
+        <f t="shared" ref="Y15:AF15" si="38">+Y14/Y16</f>
         <v>8.6329891152665361</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>15.286549480431194</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="41"/>
+        <f t="shared" si="38"/>
         <v>24.606885666370722</v>
-      </c>
-      <c r="AB15" s="2">
-        <f t="shared" si="41"/>
-        <v>29.837192068659352</v>
-      </c>
-      <c r="AC15" s="2">
-        <f t="shared" si="41"/>
-        <v>41.200795722600354</v>
-      </c>
-      <c r="AD15" s="2">
-        <f t="shared" si="41"/>
-        <v>55.08209198966162</v>
-      </c>
-      <c r="AE15" s="2">
-        <f t="shared" si="41"/>
-        <v>72.204600013709765</v>
-      </c>
-      <c r="AF15" s="2">
-        <f t="shared" si="41"/>
-        <v>87.945945388547386</v>
-      </c>
-      <c r="AG15" s="2">
-        <f t="shared" ref="AG15" si="42">+AG14/AG16</f>
-        <v>106.57128483313404</v>
       </c>
     </row>
     <row r="16" spans="1:65" x14ac:dyDescent="0.2">
@@ -2503,6 +2507,9 @@
       <c r="P16" s="2">
         <v>2517</v>
       </c>
+      <c r="R16" s="2">
+        <v>2534</v>
+      </c>
       <c r="U16" s="2" t="s">
         <v>34</v>
       </c>
@@ -2524,30 +2531,6 @@
         <f>AVERAGE(J16:M16)</f>
         <v>2534.25</v>
       </c>
-      <c r="AB16" s="2">
-        <f t="shared" ref="AB16:AG16" si="43">+AA16</f>
-        <v>2534.25</v>
-      </c>
-      <c r="AC16" s="2">
-        <f t="shared" si="43"/>
-        <v>2534.25</v>
-      </c>
-      <c r="AD16" s="2">
-        <f t="shared" si="43"/>
-        <v>2534.25</v>
-      </c>
-      <c r="AE16" s="2">
-        <f t="shared" si="43"/>
-        <v>2534.25</v>
-      </c>
-      <c r="AF16" s="2">
-        <f t="shared" si="43"/>
-        <v>2534.25</v>
-      </c>
-      <c r="AG16" s="2">
-        <f t="shared" si="43"/>
-        <v>2534.25</v>
-      </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
@@ -2557,7 +2540,7 @@
         <v>35</v>
       </c>
       <c r="V17" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18" spans="1:33" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -2565,55 +2548,63 @@
         <v>32</v>
       </c>
       <c r="F18" s="7">
-        <f t="shared" ref="F18:H18" si="44">+F5/B5-1</f>
-        <v>2.8945806510523697E-2</v>
+        <f t="shared" ref="F18:P18" si="39">+F3/B3-1</f>
+        <v>2.6408198366060009E-2</v>
       </c>
       <c r="G18" s="7">
-        <f t="shared" si="44"/>
-        <v>0.1025814642403724</v>
+        <f t="shared" si="39"/>
+        <v>0.11022829782804799</v>
       </c>
       <c r="H18" s="7">
-        <f t="shared" si="44"/>
-        <v>0.26993363033002993</v>
+        <f t="shared" si="39"/>
+        <v>0.23208486685429741</v>
       </c>
       <c r="I18" s="7">
-        <f>+I5/E5-1</f>
-        <v>0.36035922615300686</v>
+        <f t="shared" si="39"/>
+        <v>0.24703870666873939</v>
       </c>
       <c r="J18" s="7">
-        <f t="shared" ref="J18:K18" si="45">+J5/F5-1</f>
-        <v>0.32293561698540185</v>
+        <f t="shared" si="39"/>
+        <v>0.27264793157619138</v>
       </c>
       <c r="K18" s="7">
-        <f t="shared" si="45"/>
-        <v>0.21912182390419899</v>
+        <f t="shared" si="39"/>
+        <v>0.2210069064658271</v>
       </c>
       <c r="L18" s="7">
-        <f t="shared" ref="L18:O18" si="46">+L5/H5-1</f>
-        <v>0.18893184421534936</v>
+        <f t="shared" si="39"/>
+        <v>0.18868974404029748</v>
       </c>
       <c r="M18" s="7">
-        <f t="shared" si="46"/>
-        <v>0.21995310957551828</v>
+        <f t="shared" si="39"/>
+        <v>0.20627757971628724</v>
       </c>
       <c r="N18" s="7">
-        <f t="shared" si="46"/>
-        <v>0.16525238973670975</v>
+        <f t="shared" si="39"/>
+        <v>0.16071869428062002</v>
       </c>
       <c r="O18" s="7">
-        <f t="shared" si="46"/>
-        <v>0.22863079683908949</v>
+        <f t="shared" si="39"/>
+        <v>0.21614496685521223</v>
       </c>
       <c r="P18" s="7">
-        <f t="shared" ref="P18" si="47">+P5/L5-1</f>
-        <v>0.26561088697537194</v>
+        <f t="shared" si="39"/>
+        <v>0.26246027248761972</v>
+      </c>
+      <c r="Q18" s="7">
+        <f>+Q3/M3-1</f>
+        <v>0.23784230649994842</v>
+      </c>
+      <c r="R18" s="7">
+        <f>+R3/N3-1</f>
+        <v>0.33078886420570019</v>
       </c>
       <c r="U18" s="7" t="s">
         <v>36</v>
       </c>
       <c r="V18" s="9">
         <f>NPV(V17,Y14:BM14)</f>
-        <v>2389398.2515990245</v>
+        <v>2078826.2123905655</v>
       </c>
       <c r="Y18" s="7" t="s">
         <v>9</v>
@@ -2628,26 +2619,26 @@
       </c>
       <c r="AB18" s="7">
         <f>+AB3/AA1-1</f>
+        <v>0.2414350770812177</v>
+      </c>
+      <c r="AC18" s="7">
+        <f t="shared" ref="AC18:AG18" si="40">+AC3/AB3-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AC18" s="7">
-        <f t="shared" ref="AC18:AG18" si="48">+AC3/AB3-1</f>
+      <c r="AD18" s="7">
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AD18" s="7">
-        <f t="shared" si="48"/>
+      <c r="AE18" s="7">
+        <f t="shared" si="40"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AE18" s="7">
-        <f t="shared" si="48"/>
-        <v>0.19999999999999996</v>
-      </c>
       <c r="AF18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="40"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AG18" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="40"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
@@ -2656,23 +2647,23 @@
         <v>99</v>
       </c>
       <c r="F19" s="8">
-        <f t="shared" ref="F19:J19" si="49">+F14/B14-1</f>
+        <f t="shared" ref="F19:J19" si="41">+F14/B14-1</f>
         <v>-0.23523107836570667</v>
       </c>
       <c r="G19" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="41"/>
         <v>0.16464782413638401</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="41"/>
         <v>1.6354948805460752</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="41"/>
         <v>2.0131126397248496</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="41"/>
         <v>1.16657908565423</v>
       </c>
       <c r="K19" s="8">
@@ -2696,8 +2687,19 @@
         <v>0.36182695878202753</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="50">+P14/L14-1</f>
+        <f t="shared" ref="P19" si="42">+P14/L14-1</f>
         <v>-0.82732024477307498</v>
+      </c>
+      <c r="Q19" s="8">
+        <f t="shared" ref="Q19" si="43">+Q14/M14-1</f>
+        <v>9.2619253287263614E-2</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" ref="R19" si="44">+R14/N14-1</f>
+        <v>0.60856765200672913</v>
+      </c>
+      <c r="S19" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="U19" s="8" t="s">
         <v>47</v>
@@ -2714,32 +2716,32 @@
         <v>0.6962541488857279</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" ref="AA19:AG19" si="51">+AA14/Z14-1</f>
+        <f t="shared" ref="AA19:AG19" si="45">+AA14/Z14-1</f>
         <v>0.58469584309579825</v>
       </c>
       <c r="AB19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.21255458627325163</v>
+        <f t="shared" si="45"/>
+        <v>0.29719178960872328</v>
       </c>
       <c r="AC19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.38085365498843982</v>
+        <f t="shared" si="45"/>
+        <v>0.34475091701519323</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.33691815955502991</v>
+        <f t="shared" si="45"/>
+        <v>0.31682460967981507</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.31085435221418023</v>
+        <f t="shared" si="45"/>
+        <v>0.29626508629773785</v>
       </c>
       <c r="AF19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.21801028427342239</v>
+        <f t="shared" si="45"/>
+        <v>0.20575912470615454</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="51"/>
-        <v>0.21178167296172035</v>
+        <f t="shared" si="45"/>
+        <v>0.19964243489180089</v>
       </c>
     </row>
     <row r="20" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2748,44 +2750,44 @@
       </c>
       <c r="V20" s="10">
         <f>+V18-V19</f>
-        <v>2371159.2515990245</v>
+        <v>2060587.2123905655</v>
       </c>
     </row>
     <row r="21" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
-        <f t="shared" ref="B21:J21" si="52">+B5/B3</f>
+        <f t="shared" ref="B21:J21" si="46">+B5/B3</f>
         <v>0.78482872294682526</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.81985982929706469</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.79375045103557773</v>
       </c>
       <c r="E21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.74083631276231932</v>
       </c>
       <c r="F21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.7867690696456624</v>
       </c>
       <c r="G21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="I21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.80815736331679588</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="46"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="K21" s="8">
@@ -2809,7 +2811,7 @@
         <v>0.82130229817324696</v>
       </c>
       <c r="P21" s="8">
-        <f t="shared" ref="P21" si="53">+P5/P3</f>
+        <f t="shared" ref="P21" si="47">+P5/P3</f>
         <v>0.82034268763904605</v>
       </c>
       <c r="U21" s="8" t="s">
@@ -2817,14 +2819,14 @@
       </c>
       <c r="V21" s="10">
         <f>+V20/main!L3</f>
-        <v>941.68357887173329</v>
+        <v>818.3428166761579</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21:AF21" si="54">+Y5/Y3</f>
+        <f t="shared" ref="Y21:AF21" si="48">+Y5/Y3</f>
         <v>0.78347297378418479</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="48"/>
         <v>0.80757740861817184</v>
       </c>
       <c r="AA21" s="8">
@@ -2832,28 +2834,28 @@
         <v>0.82985547426137196</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="54"/>
-        <v>0.82920499724489305</v>
+        <f t="shared" si="48"/>
+        <v>0.83490558057373165</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" si="54"/>
-        <v>0.84343791414115199</v>
+        <f t="shared" si="48"/>
+        <v>0.84866344885925404</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" si="54"/>
-        <v>0.85648475462938922</v>
+        <f t="shared" si="48"/>
+        <v>0.86127482812098277</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" si="54"/>
-        <v>0.86844435841027356</v>
+        <f t="shared" si="48"/>
+        <v>0.87283525911090099</v>
       </c>
       <c r="AF21" s="8">
-        <f t="shared" si="54"/>
-        <v>0.87416416891417459</v>
+        <f t="shared" si="48"/>
+        <v>0.87836416088868774</v>
       </c>
       <c r="AG21" s="8">
-        <f t="shared" ref="AG21" si="55">+AG5/AG3</f>
-        <v>0.87963529200486268</v>
+        <f t="shared" ref="AG21" si="49">+AG5/AG3</f>
+        <v>0.88365267563265781</v>
       </c>
     </row>
     <row r="22" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2861,39 +2863,39 @@
         <v>42</v>
       </c>
       <c r="B22" s="8">
-        <f t="shared" ref="B22:J22" si="56">+B6/B3</f>
+        <f t="shared" ref="B22:J22" si="50">+B6/B3</f>
         <v>0.27615737422961156</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.30150579418499757</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.33087969979071952</v>
       </c>
       <c r="E22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.30377739779263174</v>
       </c>
       <c r="F22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.32749170884971202</v>
       </c>
       <c r="G22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.29200912528516515</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.27063199203420607</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.26219740220887039</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="50"/>
         <v>0.27370731038266355</v>
       </c>
       <c r="K22" s="8">
@@ -2917,21 +2919,21 @@
         <v>0.27237141173499452</v>
       </c>
       <c r="P22" s="8">
-        <f t="shared" ref="P22" si="57">+P6/P3</f>
+        <f t="shared" ref="P22" si="51">+P6/P3</f>
         <v>0.29553881581515162</v>
       </c>
       <c r="U22" s="8" t="s">
         <v>39</v>
       </c>
       <c r="V22" s="10">
-        <v>646</v>
+        <v>609</v>
       </c>
       <c r="Y22" s="8">
-        <f t="shared" ref="Y22:AF22" si="58">+Y6/Y3</f>
+        <f t="shared" ref="Y22:AF22" si="52">+Y6/Y3</f>
         <v>0.30304693462768739</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="52"/>
         <v>0.28526845612708579</v>
       </c>
       <c r="AA22" s="8">
@@ -2939,28 +2941,28 @@
         <v>0.27101355809074806</v>
       </c>
       <c r="AB22" s="8">
-        <f t="shared" si="58"/>
-        <v>0.23713686332940456</v>
+        <f t="shared" si="52"/>
+        <v>0.23577120394098475</v>
       </c>
       <c r="AC22" s="8">
-        <f t="shared" si="58"/>
-        <v>0.20749475541322898</v>
+        <f t="shared" si="52"/>
+        <v>0.21219408354688629</v>
       </c>
       <c r="AD22" s="8">
-        <f t="shared" si="58"/>
-        <v>0.18155791098657537</v>
+        <f t="shared" si="52"/>
+        <v>0.19097467519219771</v>
       </c>
       <c r="AE22" s="8">
-        <f t="shared" si="58"/>
-        <v>0.15886317211325346</v>
+        <f t="shared" si="52"/>
+        <v>0.17187720767297796</v>
       </c>
       <c r="AF22" s="8">
-        <f t="shared" si="58"/>
-        <v>0.14504898323384013</v>
+        <f t="shared" si="52"/>
+        <v>0.16141511677114453</v>
       </c>
       <c r="AG22" s="8">
-        <f t="shared" ref="AG22" si="59">+AG6/AG3</f>
-        <v>0.13243602817002795</v>
+        <f t="shared" ref="AG22" si="53">+AG6/AG3</f>
+        <v>0.15158984879377052</v>
       </c>
     </row>
     <row r="23" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -2968,39 +2970,39 @@
         <v>43</v>
       </c>
       <c r="B23" s="8">
-        <f t="shared" ref="B23:J23" si="60">+B7/B3</f>
+        <f t="shared" ref="B23:J23" si="54">+B7/B3</f>
         <v>0.11867564855955282</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.12473110818125044</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.13639315869235766</v>
       </c>
       <c r="E23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.142204259288046</v>
       </c>
       <c r="F23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>0.10626636411241054</v>
       </c>
       <c r="G23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>9.8565580174380454E-2</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>8.4255842558425581E-2</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>8.0426815586746775E-2</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="54"/>
         <v>7.0333287614867651E-2</v>
       </c>
       <c r="K23" s="8">
@@ -3024,7 +3026,7 @@
         <v>6.269467126862531E-2</v>
       </c>
       <c r="P23" s="8">
-        <f t="shared" ref="P23" si="61">+P7/P3</f>
+        <f t="shared" ref="P23" si="55">+P7/P3</f>
         <v>5.5520861793060379E-2</v>
       </c>
       <c r="U23" s="8" t="s">
@@ -3032,14 +3034,14 @@
       </c>
       <c r="V23" s="8">
         <f>+V21/V22-1</f>
-        <v>0.45771451837729615</v>
+        <v>0.34374846744853516</v>
       </c>
       <c r="Y23" s="8">
-        <f t="shared" ref="Y23:AF23" si="62">+Y7/Y3</f>
+        <f t="shared" ref="Y23:AF23" si="56">+Y7/Y3</f>
         <v>0.13087326021147597</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="56"/>
         <v>9.1185387802907317E-2</v>
       </c>
       <c r="AA23" s="8">
@@ -3047,28 +3049,28 @@
         <v>7.0094612592444344E-2</v>
       </c>
       <c r="AB23" s="8">
-        <f t="shared" si="62"/>
-        <v>6.0164542475181396E-2</v>
+        <f t="shared" si="56"/>
+        <v>5.8156445152140919E-2</v>
       </c>
       <c r="AC23" s="8">
-        <f t="shared" si="62"/>
-        <v>5.1641232291197374E-2</v>
+        <f t="shared" si="56"/>
+        <v>4.9917615422254293E-2</v>
       </c>
       <c r="AD23" s="8">
-        <f t="shared" si="62"/>
-        <v>4.4325391049944408E-2</v>
+        <f t="shared" si="56"/>
+        <v>4.2845953237434939E-2</v>
       </c>
       <c r="AE23" s="8">
-        <f t="shared" si="62"/>
-        <v>3.8045960651202283E-2</v>
+        <f t="shared" si="56"/>
+        <v>3.6776109862131659E-2</v>
       </c>
       <c r="AF23" s="8">
-        <f t="shared" si="62"/>
-        <v>3.4075947365859442E-2</v>
+        <f t="shared" si="56"/>
+        <v>3.2938602746083144E-2</v>
       </c>
       <c r="AG23" s="8">
-        <f t="shared" ref="AG23" si="63">+AG7/AG3</f>
-        <v>3.0520196336378456E-2</v>
+        <f t="shared" ref="AG23" si="57">+AG7/AG3</f>
+        <v>2.950153115518751E-2</v>
       </c>
     </row>
     <row r="24" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3076,39 +3078,39 @@
         <v>44</v>
       </c>
       <c r="B24" s="8">
-        <f t="shared" ref="B24:J24" si="64">+B8/B3</f>
+        <f t="shared" ref="B24:J24" si="58">+B8/B3</f>
         <v>8.4563566002579901E-2</v>
       </c>
       <c r="C24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>0.1036361113038651</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>0.12210435159125352</v>
       </c>
       <c r="E24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>9.5911705269703093E-2</v>
       </c>
       <c r="F24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>0.10071565718275441</v>
       </c>
       <c r="G24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>0.13012906653332917</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>6.062203479177649E-2</v>
       </c>
       <c r="I24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>5.7066640073795215E-2</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="58"/>
         <v>9.4774379371828282E-2</v>
       </c>
       <c r="K24" s="8">
@@ -3132,15 +3134,15 @@
         <v>5.6044279821533802E-2</v>
       </c>
       <c r="P24" s="8">
-        <f t="shared" ref="P24" si="65">+P8/P3</f>
+        <f t="shared" ref="P24" si="59">+P8/P3</f>
         <v>6.8537527809218998E-2</v>
       </c>
       <c r="Y24" s="8">
-        <f t="shared" ref="Y24:AF24" si="66">+Y8/Y3</f>
+        <f t="shared" ref="Y24:AF24" si="60">+Y8/Y3</f>
         <v>0.10133008601394404</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="60"/>
         <v>8.4565718563983955E-2</v>
       </c>
       <c r="AA24" s="8">
@@ -3148,28 +3150,28 @@
         <v>6.0161402312312984E-2</v>
       </c>
       <c r="AB24" s="8">
-        <f t="shared" si="66"/>
-        <v>5.0134501926927491E-2</v>
+        <f t="shared" si="60"/>
+        <v>4.9915010076381459E-2</v>
       </c>
       <c r="AC24" s="8">
-        <f t="shared" si="66"/>
-        <v>4.1778751605772914E-2</v>
+        <f t="shared" si="60"/>
+        <v>4.2843716982227421E-2</v>
       </c>
       <c r="AD24" s="8">
-        <f t="shared" si="66"/>
-        <v>3.4815626338144091E-2</v>
+        <f t="shared" si="60"/>
+        <v>3.6774190409745208E-2</v>
       </c>
       <c r="AE24" s="8">
-        <f t="shared" si="66"/>
-        <v>2.901302194845341E-2</v>
+        <f t="shared" si="60"/>
+        <v>3.1564513435031305E-2</v>
       </c>
       <c r="AF24" s="8">
-        <f t="shared" si="66"/>
-        <v>2.5228714737785575E-2</v>
+        <f t="shared" si="60"/>
+        <v>2.8270825076593262E-2</v>
       </c>
       <c r="AG24" s="8">
-        <f t="shared" ref="AG24" si="67">+AG8/AG3</f>
-        <v>2.1938012815465719E-2</v>
+        <f t="shared" ref="AG24" si="61">+AG8/AG3</f>
+        <v>2.532082593816614E-2</v>
       </c>
     </row>
     <row r="25" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3177,39 +3179,39 @@
         <v>41</v>
       </c>
       <c r="B25" s="8">
-        <f t="shared" ref="B25:J25" si="68">+B10/B3</f>
+        <f t="shared" ref="B25:J25" si="62">+B10/B3</f>
         <v>0.30543213415508097</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.28998681562695161</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.20437324096124701</v>
       </c>
       <c r="E25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.19894295041193844</v>
       </c>
       <c r="F25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.25229533950078548</v>
       </c>
       <c r="G25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.40262402624026239</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.4084665054473835</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="62"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="K25" s="8">
@@ -3233,15 +3235,15 @@
         <v>0.43019193534809325</v>
       </c>
       <c r="P25" s="8">
-        <f t="shared" ref="P25" si="69">+P10/P3</f>
+        <f t="shared" ref="P25" si="63">+P10/P3</f>
         <v>0.4007454822216151</v>
       </c>
       <c r="Y25" s="8">
-        <f t="shared" ref="Y25:AF25" si="70">+Y10/Y3</f>
+        <f t="shared" ref="Y25:AF25" si="64">+Y10/Y3</f>
         <v>0.24822269293107735</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="64"/>
         <v>0.34655784612419477</v>
       </c>
       <c r="AA25" s="8">
@@ -3249,28 +3251,28 @@
         <v>0.4285859012658666</v>
       </c>
       <c r="AB25" s="8">
-        <f t="shared" si="70"/>
-        <v>0.48176908951337966</v>
+        <f t="shared" si="64"/>
+        <v>0.49106292140422458</v>
       </c>
       <c r="AC25" s="8">
-        <f t="shared" si="70"/>
-        <v>0.54252317483095269</v>
+        <f t="shared" si="64"/>
+        <v>0.54370803290788605</v>
       </c>
       <c r="AD25" s="8">
-        <f t="shared" si="70"/>
-        <v>0.59578582625472543</v>
+        <f t="shared" si="64"/>
+        <v>0.59068000928160491</v>
       </c>
       <c r="AE25" s="8">
-        <f t="shared" si="70"/>
-        <v>0.64252220369736446</v>
+        <f t="shared" si="64"/>
+        <v>0.63261742814076005</v>
       </c>
       <c r="AF25" s="8">
-        <f t="shared" si="70"/>
-        <v>0.66981052357668946</v>
+        <f t="shared" si="64"/>
+        <v>0.65573961629486688</v>
       </c>
       <c r="AG25" s="8">
-        <f t="shared" ref="AG25" si="71">+AG10/AG3</f>
-        <v>0.69474105468299052</v>
+        <f t="shared" ref="AG25" si="65">+AG10/AG3</f>
+        <v>0.67724046974553365</v>
       </c>
     </row>
     <row r="26" spans="1:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3278,39 +3280,39 @@
         <v>45</v>
       </c>
       <c r="B26" s="8">
-        <f t="shared" ref="B26:J26" si="72">+B13/B12</f>
+        <f t="shared" ref="B26:J26" si="66">+B13/B12</f>
         <v>0.1619892231701841</v>
       </c>
       <c r="C26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.18311751771316884</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.21180057388809181</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.24345422019840623</v>
       </c>
       <c r="F26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.21869440262761736</v>
       </c>
       <c r="G26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="I26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.16605188005711566</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="66"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="K26" s="8">
@@ -3334,43 +3336,43 @@
         <v>0.10699327943897925</v>
       </c>
       <c r="P26" s="8">
-        <f t="shared" ref="P26" si="73">+P13/P12</f>
+        <f t="shared" ref="P26" si="67">+P13/P12</f>
         <v>0.87494806813460735</v>
       </c>
       <c r="Y26" s="8">
-        <f t="shared" ref="Y26:AF26" si="74">+Y13/Y12</f>
+        <f t="shared" ref="Y26:AF26" si="68">+Y13/Y12</f>
         <v>0.19501023630243935</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.17471855443517942</v>
       </c>
       <c r="AA26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.11751386844786596</v>
       </c>
       <c r="AB26" s="8">
-        <f t="shared" si="74"/>
-        <v>0.19999999999999998</v>
+        <f t="shared" si="68"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AC26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.2</v>
       </c>
       <c r="AD26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.2</v>
       </c>
       <c r="AE26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.2</v>
       </c>
       <c r="AF26" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="68"/>
         <v>0.2</v>
       </c>
       <c r="AG26" s="8">
-        <f t="shared" ref="AG26" si="75">+AG13/AG12</f>
+        <f t="shared" ref="AG26" si="69">+AG13/AG12</f>
         <v>0.2</v>
       </c>
     </row>
@@ -3379,71 +3381,71 @@
         <v>46</v>
       </c>
       <c r="B27" s="7">
-        <f t="shared" ref="B27:K27" si="76">+B14/B3</f>
+        <f t="shared" ref="B27:K27" si="70">+B14/B3</f>
         <v>0.26748602551239786</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.23201026993269031</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.15858410911452694</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.1446292554018343</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.19930179787048349</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.24338260570642833</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.33921982076963625</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.34945526164892421</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.33929502125908656</v>
       </c>
       <c r="K27" s="7">
-        <f t="shared" si="76"/>
+        <f t="shared" si="70"/>
         <v>0.34462900872770086</v>
       </c>
       <c r="L27" s="7">
-        <f t="shared" ref="L27:M27" si="77">+L14/L3</f>
+        <f t="shared" ref="L27:M27" si="71">+L14/L3</f>
         <v>0.38650865998176848</v>
       </c>
       <c r="M27" s="7">
-        <f t="shared" si="77"/>
+        <f t="shared" si="71"/>
         <v>0.43067066239537044</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" ref="N27:O27" si="78">+N14/N3</f>
+        <f t="shared" ref="N27:O27" si="72">+N14/N3</f>
         <v>0.39334499220116276</v>
       </c>
       <c r="O27" s="7">
-        <f t="shared" si="78"/>
+        <f t="shared" si="72"/>
         <v>0.38591211381429413</v>
       </c>
       <c r="P27" s="7">
-        <f t="shared" ref="P27" si="79">+P14/P3</f>
+        <f t="shared" ref="P27" si="73">+P14/P3</f>
         <v>5.2866788962179459E-2</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" ref="Y27:AF27" si="80">+Y14/Y3</f>
+        <f t="shared" ref="Y27:AF27" si="74">+Y14/Y3</f>
         <v>0.19894690804311846</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="80"/>
+        <f t="shared" si="74"/>
         <v>0.29170576941609033</v>
       </c>
       <c r="AA27" s="7">
@@ -3451,28 +3453,28 @@
         <v>0.3852207668339499</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="80"/>
-        <v>0.38925100629350401</v>
+        <f t="shared" si="74"/>
+        <v>0.40252223023909633</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="80"/>
-        <v>0.44791556229026103</v>
+        <f t="shared" si="74"/>
+        <v>0.45107678186085459</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="80"/>
-        <v>0.49902204097762676</v>
+        <f t="shared" si="74"/>
+        <v>0.49499083934128923</v>
       </c>
       <c r="AE27" s="7">
-        <f t="shared" si="80"/>
-        <v>0.54512101188860418</v>
+        <f t="shared" si="74"/>
+        <v>0.53469945256277163</v>
       </c>
       <c r="AF27" s="7">
-        <f t="shared" si="80"/>
-        <v>0.57735912926422128</v>
+        <f t="shared" si="74"/>
+        <v>0.56062499469821525</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" ref="AG27" si="81">+AG14/AG3</f>
-        <v>0.60837670570393065</v>
+        <f t="shared" ref="AG27" si="75">+AG14/AG3</f>
+        <v>0.5848256814791043</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.2">
@@ -3490,51 +3492,51 @@
         <v>64</v>
       </c>
       <c r="B33" s="3">
-        <f t="shared" ref="B33:K33" si="82">+B36-B46</f>
+        <f t="shared" ref="B33:K33" si="76">+B36-B46</f>
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="F33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="G33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="H33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="I33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <f t="shared" si="82"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="M33" s="3">
-        <f t="shared" ref="M33:N33" si="83">+M36-M46</f>
+        <f t="shared" ref="M33:N33" si="77">+M36-M46</f>
         <v>48989</v>
       </c>
       <c r="N33" s="3">
-        <f t="shared" si="83"/>
+        <f t="shared" si="77"/>
         <v>41401</v>
       </c>
       <c r="O33" s="3">
@@ -3557,72 +3559,72 @@
         <v>80988</v>
       </c>
       <c r="AB33" s="3">
-        <f t="shared" ref="AB33:AR33" si="84">+AA33+AB14</f>
-        <v>156602.90399999998</v>
+        <f t="shared" ref="AB33:AR33" si="78">+AA33+AB14</f>
+        <v>161880.88</v>
       </c>
       <c r="AC33" s="3">
-        <f t="shared" si="84"/>
-        <v>261016.02055999992</v>
+        <f t="shared" si="78"/>
+        <v>270661.65456</v>
       </c>
       <c r="AD33" s="3">
-        <f t="shared" si="84"/>
-        <v>400607.81218479987</v>
+        <f t="shared" si="78"/>
+        <v>413906.85556063993</v>
       </c>
       <c r="AE33" s="3">
-        <f t="shared" si="84"/>
-        <v>583592.31976954383</v>
+        <f t="shared" si="78"/>
+        <v>599590.60839747125</v>
       </c>
       <c r="AF33" s="3">
-        <f t="shared" si="84"/>
-        <v>806469.33187047008</v>
+        <f t="shared" si="78"/>
+        <v>823480.48769016296</v>
       </c>
       <c r="AG33" s="3">
-        <f t="shared" si="84"/>
-        <v>1076547.6104588402</v>
+        <f t="shared" si="78"/>
+        <v>1092068.2876324789</v>
       </c>
       <c r="AH33" s="3">
-        <f t="shared" si="84"/>
-        <v>1343925.1062613265</v>
+        <f t="shared" si="78"/>
+        <v>1357970.2095753718</v>
       </c>
       <c r="AI33" s="3">
-        <f t="shared" si="84"/>
-        <v>1608628.8271057878</v>
+        <f t="shared" si="78"/>
+        <v>1621213.1122988358</v>
       </c>
       <c r="AJ33" s="3">
-        <f t="shared" si="84"/>
-        <v>1870685.5107418047</v>
+        <f t="shared" si="78"/>
+        <v>1881823.585995065</v>
       </c>
       <c r="AK33" s="3">
-        <f t="shared" si="84"/>
-        <v>2130121.6275414615</v>
+        <f t="shared" si="78"/>
+        <v>2139827.9549543322</v>
       </c>
       <c r="AL33" s="3">
-        <f t="shared" si="84"/>
-        <v>2386963.3831731216</v>
+        <f t="shared" si="78"/>
+        <v>2395252.2802240066</v>
       </c>
       <c r="AM33" s="3">
-        <f t="shared" si="84"/>
-        <v>2641236.7212484651</v>
+        <f t="shared" si="78"/>
+        <v>2648122.3622409841</v>
       </c>
       <c r="AN33" s="3">
-        <f t="shared" si="84"/>
-        <v>2892967.3259430551</v>
+        <f t="shared" si="78"/>
+        <v>2898463.7434377917</v>
       </c>
       <c r="AO33" s="3">
-        <f t="shared" si="84"/>
-        <v>3142180.6245906991</v>
+        <f t="shared" si="78"/>
+        <v>3146301.7108226316</v>
       </c>
       <c r="AP33" s="3">
-        <f t="shared" si="84"/>
-        <v>3388901.7902518669</v>
+        <f t="shared" si="78"/>
+        <v>3391661.2985336231</v>
       </c>
       <c r="AQ33" s="3">
-        <f t="shared" si="84"/>
-        <v>3633155.7442564229</v>
+        <f t="shared" si="78"/>
+        <v>3634567.2903675046</v>
       </c>
       <c r="AR33" s="3">
-        <f t="shared" si="84"/>
-        <v>3874967.1587209334</v>
+        <f t="shared" si="78"/>
+        <v>3875044.2222830472</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.2">
@@ -4139,55 +4141,55 @@
         <v>74</v>
       </c>
       <c r="B62" s="2">
-        <f t="shared" ref="B62:N62" si="85">+B14</f>
+        <f t="shared" ref="B62:N62" si="79">+B14</f>
         <v>7465</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>6687</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>4395</v>
       </c>
       <c r="E62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>4652</v>
       </c>
       <c r="F62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>5709</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>7788</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>11583</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>14017</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>12369</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>13465</v>
       </c>
       <c r="L62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>15688</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>20838</v>
       </c>
       <c r="N62" s="2">
-        <f t="shared" si="85"/>
+        <f t="shared" si="79"/>
         <v>16644</v>
       </c>
       <c r="O62" s="2">
@@ -4583,15 +4585,15 @@
         <v>102</v>
       </c>
       <c r="L95" s="2">
-        <f t="shared" ref="L95:N95" si="86">+L75-L94</f>
+        <f t="shared" ref="L95:N95" si="80">+L75-L94</f>
         <v>16466</v>
       </c>
       <c r="M95" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="80"/>
         <v>13563</v>
       </c>
       <c r="N95" s="2">
-        <f t="shared" si="86"/>
+        <f t="shared" si="80"/>
         <v>11085</v>
       </c>
       <c r="O95" s="2">
@@ -4611,6 +4613,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="de0fd296-9832-4e10-a7ad-2bcee574d3b0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010078CBFEB144F63F4E9EB43CF067A3FDD2" ma:contentTypeVersion="9" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="f59182e7d3e0cf5298e8ad942a121699">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="de0fd296-9832-4e10-a7ad-2bcee574d3b0" xmlns:ns4="02570eab-4ecf-4bb5-b806-a666b23f79b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f61c57c9eb7d1a1f1952f23e1a76f510" ns3:_="" ns4:_="">
     <xsd:import namespace="de0fd296-9832-4e10-a7ad-2bcee574d3b0"/>
@@ -4805,24 +4824,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34E1E6AC-BE1F-4454-ACC0-808E93021859}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="02570eab-4ecf-4bb5-b806-a666b23f79b6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="de0fd296-9832-4e10-a7ad-2bcee574d3b0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="de0fd296-9832-4e10-a7ad-2bcee574d3b0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3CAFD1E-70C1-468B-BCA7-27CB3B3A9D77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20302561-F91D-4714-9836-447F718E17F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4839,29 +4866,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3CAFD1E-70C1-468B-BCA7-27CB3B3A9D77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34E1E6AC-BE1F-4454-ACC0-808E93021859}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="02570eab-4ecf-4bb5-b806-a666b23f79b6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="de0fd296-9832-4e10-a7ad-2bcee574d3b0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>